--- a/reports/grove/2026-03/grove_settlement_march_2026.xlsx
+++ b/reports/grove/2026-03/grove_settlement_march_2026.xlsx
@@ -11,8 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off-protocol holdings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDE daily" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDE daily" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -76,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -89,6 +90,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +489,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>495038.8350685022</v>
+        <v>1056301.355068502</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +505,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>501325.9540337168</v>
+        <v>1062588.474033717</v>
       </c>
     </row>
     <row r="8">
@@ -601,7 +603,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>495038.8350685022</v>
+        <v>1056301.355068502</v>
       </c>
     </row>
     <row r="20">
@@ -617,7 +619,7 @@
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="4" t="n">
-        <v>-2561771.900811452</v>
+        <v>-2000509.380811452</v>
       </c>
     </row>
     <row r="23">
@@ -652,7 +654,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-05T11:08:05+00:00</t>
+          <t>2026-06-08T08:17:46+00:00</t>
         </is>
       </c>
     </row>
@@ -679,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2054,12 +2056,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2069,7 +2071,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
@@ -2119,12 +2121,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2134,7 +2136,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2184,12 +2186,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (alt holder idle)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2249,12 +2251,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDC raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2314,12 +2316,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2357,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" s="5" t="n">
         <v>0</v>
@@ -2374,21 +2376,17 @@
       <c r="R25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2398,7 +2396,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
@@ -2426,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>0</v>
@@ -2443,17 +2441,21 @@
       <c r="R26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
+          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2513,12 +2515,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>E24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle)</t>
+          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2528,7 +2530,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -2578,17 +2580,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E27</t>
+          <t>E26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USDC raw on Base (ALM idle)</t>
+          <t>PYUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2643,59 +2645,189 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>E27</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>USDC raw on Base (ALM idle)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>E38</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Agora AUSD incentives (cash distribution to Grove Eth ALM)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>561262.52</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>561262.52</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>561262.52</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
@@ -3141,6 +3273,1671 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Daily ilk debt + Sky charge breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>cum_debt</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>− ALM idle</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>− PSM USDS</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>− SDE NAV</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>− Curve idle</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>− Lending idle</t>
+        </is>
+      </c>
+      <c r="H5" s="2">
+        <f> utilized</f>
+        <v/>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>SSR APY</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>base APY</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>T (months)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>ref_rate APY</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>sub APY</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge (gross on cum_debt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2374020522.216694</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1316496454.413348</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1057524067.803346</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>0.037235</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>106819.0109481043</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>259094.9587634011</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2425226752.705742</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1366751074.217681</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1058475678.488061</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>0.03714333333333333</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>106686.920529731</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>264775.6981761664</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>2425226752.705742</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1366839855.528716</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1058386897.177026</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>0.03714333333333333</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>106676.651411086</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>264775.6981761664</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>2435226752.705742</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1366940267.40807</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1068286485.297672</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>0.03714333333333333</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>107821.7127281893</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>265932.3738915078</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>2421231752.705742</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1367037747.422105</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1054194005.283637</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>0.03714333333333333</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>106191.6697880725</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>264313.6062278875</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2371238376.923146</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1367138364.218488</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1004100012.704658</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>0.03714333333333333</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>100397.4193180128</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>258530.993858321</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2371238376.923146</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1367138364.218488</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1004100012.704658</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0.03714333333333333</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>100397.4193180128</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>258530.993858321</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2371238376.923146</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1367138364.218488</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1004100012.704658</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>0.03714333333333333</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>100397.4193180128</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>258530.993858321</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2351242376.923146</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1367436392.527869</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>983805984.3952771</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>0.03675104166666666</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>97285.22981550643</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>246270.6908626946</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>2400317530.323146</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1367527321.087601</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1032790209.235545</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>0.03675104166666666</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>102463.1281974038</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>251623.4661630356</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2128458956.668021</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1367624655.7615</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>760834300.9065213</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>0.03675104166666666</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>75236.31792167661</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>221971.0299009191</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>2173459306.781233</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1092722390.859259</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1080736915.921974</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>0.03675104166666666</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>107692.8204042103</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>226879.3540915613</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2219029306.781233</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1238392251.330077</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>980637055.451156</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>0.03675104166666666</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>96971.86520349166</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>231849.8117169987</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2219029306.781233</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1238392251.330077</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>980637055.451156</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0.03675104166666666</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>96971.86520349166</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>231849.8117169987</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>2219029306.781233</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>1238392251.330077</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>980637055.451156</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0.03675104166666666</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>96971.86520349166</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>231849.8117169987</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2269029306.781233</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>1238733997.442723</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>1030295309.33851</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>0.03656770833333333</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>101706.4332561505</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>236818.8941619598</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2328029551.415538</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1288842042.188964</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>1039187509.226574</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>0.03656770833333333</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>102676.3323726864</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>243254.2291596612</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>2378029551.415538</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>1338965154.153005</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>1039064397.262533</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>0.03656770833333333</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>102662.9041786892</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>248707.8802738124</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>2378039549.415538</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1389064336.420757</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>988975212.9947814</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0.03656770833333333</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>97317.17085855019</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>248708.9707858892</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2378039549.415538</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>1439158172.528966</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>938881376.8865719</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>0.03656770833333333</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>92387.83557951872</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>248708.9707858892</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>2378039549.415538</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1439158172.528966</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>938881376.8865719</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0.03656770833333333</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>92387.83557951872</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>248708.9707858892</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2392039549.415538</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>1439158172.528966</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>952881376.8865719</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0.03656770833333333</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>93765.46403179712</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>250235.9930978515</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2493039549.415538</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1489563132.264409</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1003476417.151129</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0.036384375</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>98296.56148550739</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>260767.7142029541</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2543039549.415538</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>1564713833.521337</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>978325715.8942013</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>0.036384375</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>95795.08908697993</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>266221.3653171053</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2593039549.415538</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1614837843.227145</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>978201706.1883926</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.036384375</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>95782.94638172074</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>271675.0164312565</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>2621953033.083677</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>1664994792.231503</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>956958240.8521742</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>0.036384375</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>93702.8419529629</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>274828.6974796713</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2681953033.083677</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>1715130043.920879</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>966822989.1627984</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0.036384375</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>94668.77224374867</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>281373.0788166527</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2686953033.083677</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>1715130043.920879</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>971822989.1627984</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>0.036384375</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>95158.35913454926</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>281918.4439280678</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2686953033.083677</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>1715130043.920879</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>971822989.1627984</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0.036384375</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>95158.35913454926</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>281918.4439280678</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>2792299936.006419</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>1765624791.053028</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>1026675144.953391</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>0.03620104166666667</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>100342.1771880477</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>292924.209366034</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>2851300105.715095</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>1865795252.54971</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>985504853.1653847</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" s="6" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>0.03620104166666667</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>96020.33810648411</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>299359.5361913706</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Σ daily charges</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="n">
+        <v>3056810.735879954</v>
+      </c>
+      <c r="O38" s="10" t="n">
+        <v>7972909.707691432</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3434,7 +5231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/reports/grove/2026-03/grove_settlement_march_2026.xlsx
+++ b/reports/grove/2026-03/grove_settlement_march_2026.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-08T08:17:46+00:00</t>
+          <t>2026-06-09T00:21:59+00:00</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-03/grove_settlement_march_2026.xlsx
+++ b/reports/grove/2026-03/grove_settlement_march_2026.xlsx
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1056301.355068502</v>
+        <v>1056301.360503078</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>1062588.474033717</v>
+        <v>1062588.479468293</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1056301.355068502</v>
+        <v>1056301.360503078</v>
       </c>
     </row>
     <row r="20">
@@ -619,7 +619,7 @@
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="4" t="n">
-        <v>-2000509.380811452</v>
+        <v>-2000509.375376876</v>
       </c>
     </row>
     <row r="23">
@@ -654,7 +654,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T00:21:59+00:00</t>
+          <t>2026-06-09T16:55:11+00:00</t>
         </is>
       </c>
     </row>
@@ -989,13 +989,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>797387.2735701434</v>
+        <v>797387.2735702854</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>797387.2735701434</v>
+        <v>797387.2735702854</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>-811835.8898298125</v>
+        <v>-811835.8898299544</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1054,13 +1054,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>561903.6794933636</v>
+        <v>561903.6794934636</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>561903.6794933636</v>
+        <v>561903.6794934636</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-418094.8308318345</v>
+        <v>-418094.8308319346</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1119,13 +1119,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>420075.8510001024</v>
+        <v>420075.8510001772</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>420075.8510001024</v>
+        <v>420075.8510001772</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>-276870.7152789099</v>
+        <v>-276870.7152789847</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1184,13 +1184,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>312894.4189954103</v>
+        <v>312894.418995466</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>312894.4189954103</v>
+        <v>312894.418995466</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-184970.6189954103</v>
+        <v>-184970.618995466</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1249,13 +1249,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>158383.7277207868</v>
+        <v>158383.727720815</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>158383.7277207868</v>
+        <v>158383.727720815</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-509833.721399908</v>
+        <v>-509833.7213999361</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>155198.3807401403</v>
+        <v>155198.380740168</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>155198.3807401403</v>
+        <v>155198.380740168</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>208385.6992598598</v>
+        <v>208385.6992598322</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1383,13 +1383,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>77624.14306481868</v>
+        <v>77624.1430648325</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>77624.14306481868</v>
+        <v>77624.1430648325</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>-70380.59799081869</v>
+        <v>-70380.5979908325</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1448,13 +1448,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>77600.57094439845</v>
+        <v>77600.57094441226</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>77600.57094439845</v>
+        <v>77600.57094441226</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-77106.40015109949</v>
+        <v>-77106.4001511133</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1513,13 +1513,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>400862.4808000124</v>
+        <v>400862.4808000837</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>-76551.9024220453</v>
+        <v>-76551.90242197394</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-400862.4808000124</v>
+        <v>-400862.4808000837</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>212949426.0434853</v>
@@ -1564,31 +1564,31 @@
         <v>2840058.940366508</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>40043.5742636084</v>
+        <v>40043.5775017722</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>40043.5742636084</v>
+        <v>40043.5775017722</v>
       </c>
       <c r="K13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>18715708.52330162</v>
+        <v>18715708.52319716</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>58092.95314441708</v>
+        <v>58092.95314410319</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>58092.95314441708</v>
+        <v>58092.95314410319</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-18049.37888080868</v>
+        <v>-18049.37564233099</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1629,31 +1629,31 @@
         <v>2951891.543486115</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>16557.16397339517</v>
+        <v>16557.16298206177</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>16557.16397339517</v>
+        <v>16557.16298206177</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>5155350.99164533</v>
+        <v>5155350.991677308</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>16002.04252100864</v>
+        <v>16002.04252111075</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>16002.04252100864</v>
+        <v>16002.04252111075</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>555.1214523865325</v>
+        <v>555.1204609510205</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1712,13 +1712,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>14715.69283126045</v>
+        <v>14715.69283126307</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>14715.69283126045</v>
+        <v>14715.69283126307</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-1540.273403170981</v>
+        <v>-1540.2734031736</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1777,13 +1777,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>3117.172647348261</v>
+        <v>3117.172647348816</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3117.172647348261</v>
+        <v>3117.172647348816</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>33.99948483481692</v>
+        <v>33.99948483426202</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1824,31 +1824,31 @@
         <v>-1012325.676838512</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>1750.534960008126</v>
+        <v>1750.538147753783</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>1750.534960008126</v>
+        <v>1750.538147753783</v>
       </c>
       <c r="K17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>521643.6388714861</v>
+        <v>521643.6387686555</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1619.164961524983</v>
+        <v>1619.164961206089</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1619.164961524983</v>
+        <v>1619.164961206089</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>131.369998483143</v>
+        <v>131.3731865476944</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1907,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>1301.929660963592</v>
+        <v>1301.929660963824</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>1301.929660963592</v>
+        <v>1301.929660963824</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-1301.929660976092</v>
+        <v>-1301.929660976324</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1972,13 +1972,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>31.25378425211854</v>
+        <v>31.2537842521241</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>31.25378425211854</v>
+        <v>31.2537842521241</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-31.25378425211854</v>
+        <v>-31.2537842521241</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2037,13 +2037,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>3.103967614802807e-09</v>
+        <v>3.103967614803359e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3.103967614802807e-09</v>
+        <v>3.103967614803359e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-3.103967614802807e-09</v>
+        <v>-3.103967614803359e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>

--- a/reports/grove/2026-03/grove_settlement_march_2026.xlsx
+++ b/reports/grove/2026-03/grove_settlement_march_2026.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:11+00:00</t>
+          <t>2026-06-09T22:25:22+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-03/grove_settlement_march_2026.xlsx
+++ b/reports/grove/2026-03/grove_settlement_march_2026.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T22:25:22+00:00</t>
+          <t>2026-06-10T10:52:07+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-03/grove_settlement_march_2026.xlsx
+++ b/reports/grove/2026-03/grove_settlement_march_2026.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T10:52:07+00:00</t>
+          <t>2026-06-10T15:01:22+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-03/grove_settlement_march_2026.xlsx
+++ b/reports/grove/2026-03/grove_settlement_march_2026.xlsx
@@ -22,10 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;&quot;−$&quot;#,##0.00;&quot;$&quot;0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;&quot;−$&quot;#,##0;&quot;$&quot;0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -77,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -85,12 +86,14 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -499,13 +502,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6287.11896521453</v>
+        <v>6287.119445470025</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>1062588.479468293</v>
+        <v>1062588.479948548</v>
       </c>
     </row>
     <row r="8">
@@ -527,7 +530,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>3056810.735879954</v>
+        <v>3056810.760658033</v>
       </c>
     </row>
     <row r="10">
@@ -543,7 +546,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>6308194.489023196</v>
+        <v>6308194.513801275</v>
       </c>
     </row>
     <row r="13">
@@ -565,7 +568,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>3056810.735879954</v>
+        <v>3056810.760658033</v>
       </c>
     </row>
     <row r="15">
@@ -575,13 +578,13 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-4916098.971811477</v>
+        <v>-4916099.3356033</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>7972909.707691432</v>
+        <v>7972910.096261334</v>
       </c>
     </row>
     <row r="18">
@@ -613,13 +616,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-3056810.735879954</v>
+        <v>-3056810.760658033</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="4" t="n">
-        <v>-2000509.375376876</v>
+        <v>-2000509.400154955</v>
       </c>
     </row>
     <row r="23">
@@ -654,7 +657,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T15:01:22+00:00</t>
+          <t>2026-06-23T21:34:39+00:00</t>
         </is>
       </c>
     </row>
@@ -989,13 +992,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>797387.2735702854</v>
+        <v>797387.2800337947</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>797387.2735702854</v>
+        <v>797387.2800337947</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>-811835.8898299544</v>
+        <v>-811835.8962934637</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1054,13 +1057,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>561903.6794934636</v>
+        <v>561903.6840481759</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>561903.6794934636</v>
+        <v>561903.6840481759</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-418094.8308319346</v>
+        <v>-418094.8353866469</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1119,13 +1122,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>420075.8510001772</v>
+        <v>420075.8544052531</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>420075.8510001772</v>
+        <v>420075.8544052531</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>-276870.7152789847</v>
+        <v>-276870.7186840606</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1184,13 +1187,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>312894.418995466</v>
+        <v>312894.4215317442</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>312894.418995466</v>
+        <v>312894.4215317442</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-184970.618995466</v>
+        <v>-184970.6215317443</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1249,13 +1252,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>158383.727720815</v>
+        <v>158383.7290046513</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>158383.727720815</v>
+        <v>158383.7290046513</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-509833.7213999361</v>
+        <v>-509833.7226837724</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1314,13 +1317,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>155198.380740168</v>
+        <v>155198.3819981842</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>155198.380740168</v>
+        <v>155198.3819981842</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>208385.6992598322</v>
+        <v>208385.6980018159</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1383,13 +1386,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>77624.1430648325</v>
+        <v>77624.1436940429</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>77624.1430648325</v>
+        <v>77624.1436940429</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>-70380.5979908325</v>
+        <v>-70380.5986200429</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1448,13 +1451,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>77600.57094441226</v>
+        <v>77600.5715734316</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>77600.57094441226</v>
+        <v>77600.5715734316</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-77106.4001511133</v>
+        <v>-77106.40078013264</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1513,13 +1516,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>400862.4808000837</v>
+        <v>400862.4840494187</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>-76551.90242197394</v>
+        <v>-76551.89917263895</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-400862.4808000837</v>
+        <v>-400862.4840494187</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>212949426.0434853</v>
@@ -1582,13 +1585,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>58092.95314410319</v>
+        <v>58092.95361499651</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>58092.95314410319</v>
+        <v>58092.95361499651</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-18049.37564233099</v>
+        <v>-18049.37611322431</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1647,13 +1650,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>16002.04252111075</v>
+        <v>16002.04265082106</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>16002.04252111075</v>
+        <v>16002.04265082106</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>555.1204609510205</v>
+        <v>555.1203312407104</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1712,13 +1715,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>14715.69283126307</v>
+        <v>14715.69295054641</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>14715.69283126307</v>
+        <v>14715.69295054641</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-1540.2734031736</v>
+        <v>-1540.273522456941</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1777,13 +1780,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>3117.172647348816</v>
+        <v>3117.17267261618</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3117.172647348816</v>
+        <v>3117.17267261618</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>33.99948483426202</v>
+        <v>33.99945956689816</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1842,13 +1845,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1619.164961206089</v>
+        <v>1619.164974330813</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1619.164961206089</v>
+        <v>1619.164974330813</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>131.3731865476944</v>
+        <v>131.3731734229706</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1907,13 +1910,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>1301.929660963824</v>
+        <v>1301.929671517083</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>1301.929660963824</v>
+        <v>1301.929671517083</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-1301.929660976324</v>
+        <v>-1301.929671529583</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1972,13 +1975,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>31.2537842521241</v>
+        <v>31.25378450546289</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>31.2537842521241</v>
+        <v>31.25378450546289</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-31.2537842521241</v>
+        <v>-31.25378450546289</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2037,13 +2040,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>3.103967614803359e-09</v>
+        <v>3.103967639963685e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3.103967614803359e-09</v>
+        <v>3.103967639963685e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-3.103967614803359e-09</v>
+        <v>-3.103967639963685e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2844,7 +2847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -2859,185 +2862,367 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Rates &amp; subsidy — effective rate charged this period</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>3056810.735879954</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>3251383.753143241</v>
+          <t>Time-weighted utilized</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>996033011.4242479</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>equals sky_revenue (total Sky take this month)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>6308194.489023196</v>
+          <t xml:space="preserve">  — first $1B (subsidised tranche)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>977923557.3838165</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — excess (full base-rate tranche)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>18109454.04043134</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base rate (BR = SSR + 30bps), period avg</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>0.04128728437554429</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reference rate (tbill_3m), period avg</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>0.03628064516129032</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>7972909.707691432</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Subsidised rate (BR*), period avg</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>0.03669555805697115</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>3056810.735879954</v>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Effective blended rate charged</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>0.03679407153085185</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-4916098.971811477</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
-        </is>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Diff vs base rate (bps)</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>-44.93212844692437</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Subsidy benefit to prime (USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>365834.9611412594</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Subsidy</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CoF at full base rate (no subsidy)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>3422645.721799293</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t xml:space="preserve">  − actual CoF (subsidy on first tranche)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>3056810.760658033</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cap_usd</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>program_start</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = subsidy benefit</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>365834.9611412594</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ramp_months</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>24</v>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Avg balance</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CoF (USD)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ref_rate_kind</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>tbill_3m</t>
-        </is>
+          <t>Subsidised (first $1B)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>977923557.3838165</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2993539.099199175</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Excess (&gt; cap)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>18109454.04043134</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>63271.66145885853</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>3056810.760658033</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>3251383.753143241</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equals sky_revenue (total Sky take this month)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>6308194.513801275</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>7972910.096261334</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>3056810.760658033</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-4916099.3356033</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Subsidy</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cap_usd</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>program_start</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ramp_months</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ref_rate_kind</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>tbill_3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>T this period</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>2 (SoM) → 2 (EoM)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>subsidised_apy = ref_rate + (base_apy − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apy</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
         </is>
@@ -3301,7 +3486,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -3411,10 +3596,10 @@
         <v>1057524067.803346</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
@@ -3423,13 +3608,13 @@
         <v>0.0367</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.037235</v>
+        <v>0.03723500015803836</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>106819.0109481043</v>
+        <v>106819.0116521084</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>259094.9587634011</v>
+        <v>259094.9660256253</v>
       </c>
     </row>
     <row r="7">
@@ -3460,10 +3645,10 @@
         <v>1058475678.488061</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -3472,13 +3657,13 @@
         <v>0.0366</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.03714333333333333</v>
+        <v>0.0371433334913717</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>106686.920529731</v>
+        <v>106686.9212384756</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>264775.6981761664</v>
+        <v>264775.7056934781</v>
       </c>
     </row>
     <row r="8">
@@ -3509,10 +3694,10 @@
         <v>1058386897.177026</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -3521,13 +3706,13 @@
         <v>0.0366</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.03714333333333333</v>
+        <v>0.0371433334913717</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>106676.651411086</v>
+        <v>106676.6521193884</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>264775.6981761664</v>
+        <v>264775.7056934781</v>
       </c>
     </row>
     <row r="9">
@@ -3558,10 +3743,10 @@
         <v>1068286485.297672</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -3570,13 +3755,13 @@
         <v>0.0366</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.03714333333333333</v>
+        <v>0.0371433334913717</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>107821.7127281893</v>
+        <v>107821.7134858072</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>265932.3738915078</v>
+        <v>265932.3814586352</v>
       </c>
     </row>
     <row r="10">
@@ -3607,10 +3792,10 @@
         <v>1054194005.283637</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -3619,13 +3804,13 @@
         <v>0.0366</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.03714333333333333</v>
+        <v>0.0371433334913717</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>106191.6697880725</v>
+        <v>106191.6704754877</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>264313.6062278875</v>
+        <v>264313.6137252979</v>
       </c>
     </row>
     <row r="11">
@@ -3656,10 +3841,10 @@
         <v>1004100012.704658</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
@@ -3668,13 +3853,13 @@
         <v>0.0366</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.03714333333333333</v>
+        <v>0.0371433334913717</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>100397.4193180128</v>
+        <v>100397.4197558812</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>258530.993858321</v>
+        <v>258531.0011066858</v>
       </c>
     </row>
     <row r="12">
@@ -3705,10 +3890,10 @@
         <v>1004100012.704658</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -3717,13 +3902,13 @@
         <v>0.0366</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.03714333333333333</v>
+        <v>0.0371433334913717</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>100397.4193180128</v>
+        <v>100397.4197558812</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>258530.993858321</v>
+        <v>258531.0011066858</v>
       </c>
     </row>
     <row r="13">
@@ -3754,10 +3939,10 @@
         <v>1004100012.704658</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.04</v>
+        <v>0.04000000189078801</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.04312</v>
+        <v>0.04312000189646037</v>
       </c>
       <c r="K13" t="n">
         <v>2</v>
@@ -3766,13 +3951,13 @@
         <v>0.0366</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.03714333333333333</v>
+        <v>0.0371433334913717</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>100397.4193180128</v>
+        <v>100397.4197558812</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>258530.993858321</v>
+        <v>258531.0011066858</v>
       </c>
     </row>
     <row r="14">
@@ -3803,10 +3988,10 @@
         <v>983805984.3952771</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K14" t="n">
         <v>2</v>
@@ -3815,13 +4000,13 @@
         <v>0.0364</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.03675104166666666</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>97285.22981550643</v>
+        <v>97285.23058815987</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>246270.6908626946</v>
+        <v>246270.7043362921</v>
       </c>
     </row>
     <row r="15">
@@ -3852,10 +4037,10 @@
         <v>1032790209.235545</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
@@ -3864,13 +4049,13 @@
         <v>0.0364</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.03675104166666666</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>102463.1281974038</v>
+        <v>102463.129290677</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>251623.4661630356</v>
+        <v>251623.480097451</v>
       </c>
     </row>
     <row r="16">
@@ -3901,10 +4086,10 @@
         <v>760834300.9065213</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
@@ -3913,13 +4098,13 @@
         <v>0.0364</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.03675104166666666</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>75236.31792167661</v>
+        <v>75236.3185192144</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>221971.0299009191</v>
+        <v>221971.0412825704</v>
       </c>
     </row>
     <row r="17">
@@ -3950,10 +4135,10 @@
         <v>1080736915.921974</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K17" t="n">
         <v>2</v>
@@ -3962,13 +4147,13 @@
         <v>0.0364</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.03675104166666666</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>107692.8204042103</v>
+        <v>107692.8219477053</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>226879.3540915613</v>
+        <v>226879.365895768</v>
       </c>
     </row>
     <row r="18">
@@ -3999,10 +4184,10 @@
         <v>980637055.451156</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -4011,13 +4196,13 @@
         <v>0.0364</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.03675104166666666</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>96971.86520349166</v>
+        <v>96971.86597365631</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>231849.8117169987</v>
+        <v>231849.8239491097</v>
       </c>
     </row>
     <row r="19">
@@ -4048,10 +4233,10 @@
         <v>980637055.451156</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
@@ -4060,13 +4245,13 @@
         <v>0.0364</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.03675104166666666</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>96971.86520349166</v>
+        <v>96971.86597365631</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>231849.8117169987</v>
+        <v>231849.8239491097</v>
       </c>
     </row>
     <row r="20">
@@ -4097,10 +4282,10 @@
         <v>980637055.451156</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K20" t="n">
         <v>2</v>
@@ -4109,13 +4294,13 @@
         <v>0.0364</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.03675104166666666</v>
+        <v>0.03675104196384631</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>96971.86520349166</v>
+        <v>96971.86597365631</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>231849.8117169987</v>
+        <v>231849.8239491097</v>
       </c>
     </row>
     <row r="21">
@@ -4146,10 +4331,10 @@
         <v>1030295309.33851</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
@@ -4158,13 +4343,13 @@
         <v>0.0362</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.03656770833333333</v>
+        <v>0.03656770863051298</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>101706.4332561505</v>
+        <v>101706.4343262186</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>236818.8941619598</v>
+        <v>236818.906863795</v>
       </c>
     </row>
     <row r="22">
@@ -4195,10 +4380,10 @@
         <v>1039187509.226574</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K22" t="n">
         <v>2</v>
@@ -4207,13 +4392,13 @@
         <v>0.0362</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.03656770833333333</v>
+        <v>0.03656770863051298</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>102676.3323726864</v>
+        <v>102676.3335262527</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>243254.2291596612</v>
+        <v>243254.2424155113</v>
       </c>
     </row>
     <row r="23">
@@ -4244,10 +4429,10 @@
         <v>1039064397.262533</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K23" t="n">
         <v>2</v>
@@ -4256,13 +4441,13 @@
         <v>0.0362</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.03656770833333333</v>
+        <v>0.03656770863051298</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>102662.9041786892</v>
+        <v>102662.9053310994</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>248707.8802738124</v>
+        <v>248707.8939991647</v>
       </c>
     </row>
     <row r="24">
@@ -4293,10 +4478,10 @@
         <v>988975212.9947814</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K24" t="n">
         <v>2</v>
@@ -4305,13 +4490,13 @@
         <v>0.0362</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.03656770833333333</v>
+        <v>0.03656770863051298</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>97317.17085855019</v>
+        <v>97317.171635483</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>248708.9707858892</v>
+        <v>248708.9845113354</v>
       </c>
     </row>
     <row r="25">
@@ -4342,10 +4527,10 @@
         <v>938881376.8865719</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K25" t="n">
         <v>2</v>
@@ -4354,13 +4539,13 @@
         <v>0.0362</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.03656770833333333</v>
+        <v>0.03656770863051298</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>92387.83557951872</v>
+        <v>92387.83631709813</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>248708.9707858892</v>
+        <v>248708.9845113354</v>
       </c>
     </row>
     <row r="26">
@@ -4391,10 +4576,10 @@
         <v>938881376.8865719</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K26" t="n">
         <v>2</v>
@@ -4403,13 +4588,13 @@
         <v>0.0362</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.03656770833333333</v>
+        <v>0.03656770863051298</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>92387.83557951872</v>
+        <v>92387.83631709813</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>248708.9707858892</v>
+        <v>248708.9845113354</v>
       </c>
     </row>
     <row r="27">
@@ -4440,10 +4625,10 @@
         <v>952881376.8865719</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K27" t="n">
         <v>2</v>
@@ -4452,13 +4637,13 @@
         <v>0.0362</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.03656770833333333</v>
+        <v>0.03656770863051298</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>93765.46403179712</v>
+        <v>93765.46478037485</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>250235.9930978515</v>
+        <v>250236.0069547584</v>
       </c>
     </row>
     <row r="28">
@@ -4489,10 +4674,10 @@
         <v>1003476417.151129</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K28" t="n">
         <v>2</v>
@@ -4501,13 +4686,13 @@
         <v>0.036</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.036384375</v>
+        <v>0.03638437529717965</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>98296.56148550739</v>
+        <v>98296.56230374491</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>260767.7142029541</v>
+        <v>260767.7290082554</v>
       </c>
     </row>
     <row r="29">
@@ -4538,10 +4723,10 @@
         <v>978325715.8942013</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
@@ -4550,13 +4735,13 @@
         <v>0.036</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.036384375</v>
+        <v>0.03638437529717965</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>95795.08908697993</v>
+        <v>95795.08985554657</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>266221.3653171053</v>
+        <v>266221.3805919088</v>
       </c>
     </row>
     <row r="30">
@@ -4587,10 +4772,10 @@
         <v>978201706.1883926</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K30" t="n">
         <v>2</v>
@@ -4599,13 +4784,13 @@
         <v>0.036</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.036384375</v>
+        <v>0.03638437529717965</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>95782.94638172074</v>
+        <v>95782.94715018995</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>271675.0164312565</v>
+        <v>271675.0321755622</v>
       </c>
     </row>
     <row r="31">
@@ -4636,10 +4821,10 @@
         <v>956958240.8521742</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
@@ -4648,13 +4833,13 @@
         <v>0.036</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.036384375</v>
+        <v>0.03638437529717965</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>93702.8419529629</v>
+        <v>93702.84270474337</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>274828.6974796713</v>
+        <v>274828.7134954759</v>
       </c>
     </row>
     <row r="32">
@@ -4685,10 +4870,10 @@
         <v>966822989.1627984</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K32" t="n">
         <v>2</v>
@@ -4697,13 +4882,13 @@
         <v>0.036</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.036384375</v>
+        <v>0.03638437529717965</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>94668.77224374867</v>
+        <v>94668.77300327882</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>281373.0788166527</v>
+        <v>281373.09539586</v>
       </c>
     </row>
     <row r="33">
@@ -4734,10 +4919,10 @@
         <v>971822989.1627984</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K33" t="n">
         <v>2</v>
@@ -4746,13 +4931,13 @@
         <v>0.036</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.036384375</v>
+        <v>0.03638437529717965</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>95158.35913454926</v>
+        <v>95158.35989800739</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>281918.4439280678</v>
+        <v>281918.4605542253</v>
       </c>
     </row>
     <row r="34">
@@ -4783,10 +4968,10 @@
         <v>971822989.1627984</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K34" t="n">
         <v>2</v>
@@ -4795,13 +4980,13 @@
         <v>0.036</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.036384375</v>
+        <v>0.03638437529717965</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>95158.35913454926</v>
+        <v>95158.35989800739</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>281918.4439280678</v>
+        <v>281918.4605542253</v>
       </c>
     </row>
     <row r="35">
@@ -4832,10 +5017,10 @@
         <v>1026675144.953391</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K35" t="n">
         <v>2</v>
@@ -4844,13 +5029,13 @@
         <v>0.0358</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.03620104166666667</v>
+        <v>0.03620104196384632</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>100342.1771880477</v>
+        <v>100342.1782243444</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>292924.209366034</v>
+        <v>292924.2269816257</v>
       </c>
     </row>
     <row r="36">
@@ -4881,10 +5066,10 @@
         <v>985504853.1653847</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K36" t="n">
         <v>2</v>
@@ -4893,17 +5078,17 @@
         <v>0.0358</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.03620104166666667</v>
+        <v>0.03620104196384632</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>96020.33810648411</v>
+        <v>96020.33888090946</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>299359.5361913706</v>
+        <v>299359.5543609764</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Σ daily charges</t>
         </is>
@@ -4921,10 +5106,10 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="10" t="n">
-        <v>3056810.735879954</v>
+        <v>3056810.760658033</v>
       </c>
       <c r="O38" s="10" t="n">
-        <v>7972909.707691432</v>
+        <v>7972910.096261334</v>
       </c>
     </row>
   </sheetData>
@@ -5262,7 +5447,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>E8 — Janus Henderson Anemoy AAA CLO (JAAA)</t>
         </is>

--- a/reports/grove/2026-03/grove_settlement_march_2026.xlsx
+++ b/reports/grove/2026-03/grove_settlement_march_2026.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -506,168 +506,178 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>1062588.479948548</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>191719.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>1254307.729948548</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>3056810.760658033</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>3056810.760658033</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>3251383.753143241</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
         <v>6308194.513801275</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>3056810.760658033</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>3056810.760658033</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>-4916099.3356033</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
         <v>7972910.096261334</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>1056301.360503078</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1056301.360503078</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B21" s="3" t="n">
         <v>-3056810.760658033</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" s="4" t="n">
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" s="4" t="n">
         <v>-2000509.400154955</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-01 → 2026-03-31 (31 days)</t>
-        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>avalanche_c=81789468, base=44106126, ethereum=24781026, monad=4, plume=58679343</t>
+          <t>2026-03-01 → 2026-03-31 (31 days)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-23T21:34:39+00:00</t>
+          <t>avalanche_c=81789468, base=44106126, ethereum=24781026, monad=4, plume=58679343</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:21:59+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/reports/grove/2026-03/grove_settlement_march_2026.xlsx
+++ b/reports/grove/2026-03/grove_settlement_march_2026.xlsx
@@ -667,7 +667,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-23T22:21:59+00:00</t>
+          <t>2026-07-03T06:32:34+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-03/grove_settlement_march_2026.xlsx
+++ b/reports/grove/2026-03/grove_settlement_march_2026.xlsx
@@ -667,7 +667,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-03T06:32:34+00:00</t>
+          <t>2026-07-07T14:51:40+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-03/grove_settlement_march_2026.xlsx
+++ b/reports/grove/2026-03/grove_settlement_march_2026.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1056301.360503078</v>
+        <v>1056301.360503091</v>
       </c>
     </row>
     <row r="5">
@@ -518,7 +518,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>1254307.729948548</v>
+        <v>1254307.729948561</v>
       </c>
     </row>
     <row r="9">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1056301.360503078</v>
+        <v>1056301.360503091</v>
       </c>
     </row>
     <row r="21">
@@ -632,7 +632,7 @@
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="4" t="n">
-        <v>-2000509.400154955</v>
+        <v>-2000509.400154942</v>
       </c>
     </row>
     <row r="24">
@@ -667,7 +667,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-07T14:51:40+00:00</t>
+          <t>2026-07-10T11:17:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1002,13 +1002,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>797387.2800337947</v>
+        <v>797465.7272499788</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>797387.2800337947</v>
+        <v>797465.7272499788</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>-811835.8962934637</v>
+        <v>-811914.3435096479</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1067,13 +1067,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>561903.6840481759</v>
+        <v>561958.9643127111</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>561903.6840481759</v>
+        <v>561958.9643127111</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-418094.8353866469</v>
+        <v>-418150.115651182</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>420075.8544052531</v>
+        <v>420117.18160245</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>420075.8544052531</v>
+        <v>420117.18160245</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>-276870.7186840606</v>
+        <v>-276912.0458812575</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1197,13 +1197,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>312894.4215317442</v>
+        <v>312925.2041852219</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>312894.4215317442</v>
+        <v>312925.2041852219</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-184970.6215317443</v>
+        <v>-185001.4041852219</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1262,13 +1262,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>158383.7290046513</v>
+        <v>158399.3108466751</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>158383.7290046513</v>
+        <v>158399.3108466751</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-509833.7226837724</v>
+        <v>-509849.3045257962</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1327,13 +1327,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>155198.3819981842</v>
+        <v>155213.6504647486</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>155198.3819981842</v>
+        <v>155213.6504647486</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>208385.6980018159</v>
+        <v>208370.4295352515</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1396,13 +1396,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>77624.1436940429</v>
+        <v>77631.78038217922</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>77624.1436940429</v>
+        <v>77631.78038217922</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>-70380.5986200429</v>
+        <v>-70388.23530817921</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1461,13 +1461,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>77600.5715734316</v>
+        <v>77608.20594253513</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>77600.5715734316</v>
+        <v>77608.20594253513</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-77106.40078013264</v>
+        <v>-77114.03514923617</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1526,13 +1526,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>400862.4840494187</v>
+        <v>400901.9210290819</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>-76551.89917263895</v>
+        <v>-76512.46219297579</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-400862.4840494187</v>
+        <v>-400901.9210290819</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>212949426.0434853</v>
@@ -1595,13 +1595,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>58092.95361499651</v>
+        <v>58098.66881839281</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>58092.95361499651</v>
+        <v>58098.66881839281</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-18049.37611322431</v>
+        <v>-18055.0913166206</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1660,13 +1660,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>16002.04265082106</v>
+        <v>16003.61693690594</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>16002.04265082106</v>
+        <v>16003.61693690594</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>555.1203312407104</v>
+        <v>553.5460451558301</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1725,13 +1725,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>14715.69295054641</v>
+        <v>14717.14068513548</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>14715.69295054641</v>
+        <v>14717.14068513548</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-1540.273522456941</v>
+        <v>-1541.721257046014</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1790,13 +1790,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>3117.17267261618</v>
+        <v>3117.479341062812</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3117.17267261618</v>
+        <v>3117.479341062812</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>33.99945956689816</v>
+        <v>33.69279112026604</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1855,13 +1855,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1619.164974330813</v>
+        <v>1619.324268299954</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1619.164974330813</v>
+        <v>1619.324268299954</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>131.3731734229706</v>
+        <v>131.2138794538295</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1902,31 +1902,31 @@
         <v>9999494.265490999</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-1.25e-08</v>
+        <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-1.25e-08</v>
+        <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>419440.4782945209</v>
+        <v>322564.3267813226</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>1301.929671517083</v>
+        <v>1001.327733388663</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>1301.929671517083</v>
+        <v>1001.327733388663</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-1301.929671529583</v>
+        <v>-1001.327733388663</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1985,13 +1985,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>31.25378450546289</v>
+        <v>31.25685926279984</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>31.25378450546289</v>
+        <v>31.25685926279984</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-31.25378450546289</v>
+        <v>-31.25685926279984</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2050,13 +2050,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>3.103967639963685e-09</v>
+        <v>3.104273009294972e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3.103967639963685e-09</v>
+        <v>3.104273009294972e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-3.103967639963685e-09</v>
+        <v>-3.104273009294972e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>

--- a/reports/grove/2026-03/grove_settlement_march_2026.xlsx
+++ b/reports/grove/2026-03/grove_settlement_march_2026.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDE daily" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="SDE daily" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3056810.760658033</v>
+        <v>3122471.434353372</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>6308194.513801275</v>
+        <v>6373855.187496614</v>
       </c>
     </row>
     <row r="14">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>3056810.760658033</v>
+        <v>3122471.434353372</v>
       </c>
     </row>
     <row r="16">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-4916099.3356033</v>
+        <v>-4917768.039640422</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>7972910.096261334</v>
+        <v>8040239.473993795</v>
       </c>
     </row>
     <row r="19">
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-3056810.760658033</v>
+        <v>-3122471.434353372</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="4" t="n">
-        <v>-2000509.400154942</v>
+        <v>-2066170.073850281</v>
       </c>
     </row>
     <row r="24">
@@ -667,7 +667,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-10T11:17:34+00:00</t>
+          <t>2026-07-31T00:10:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1002,13 +1002,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>797465.7272499788</v>
+        <v>814595.3898297144</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>797465.7272499788</v>
+        <v>814595.3898297144</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>-811914.3435096479</v>
+        <v>-829044.0060893835</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1067,13 +1067,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>561958.9643127111</v>
+        <v>574029.9124593227</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>561958.9643127111</v>
+        <v>574029.9124593227</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-418150.115651182</v>
+        <v>-430221.0637977936</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>420117.18160245</v>
+        <v>429141.3506907143</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>420117.18160245</v>
+        <v>429141.3506907143</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>-276912.0458812575</v>
+        <v>-285936.2149695218</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1197,13 +1197,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>312925.2041852219</v>
+        <v>319646.876323876</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>312925.2041852219</v>
+        <v>319646.876323876</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-185001.4041852219</v>
+        <v>-191723.076323876</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1262,13 +1262,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>158399.3108466751</v>
+        <v>161801.7476598821</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>158399.3108466751</v>
+        <v>161801.7476598821</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-509849.3045257962</v>
+        <v>-513251.7413390032</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1327,13 +1327,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>155213.6504647486</v>
+        <v>158547.6588984386</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>155213.6504647486</v>
+        <v>158547.6588984386</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>208370.4295352515</v>
+        <v>205036.4211015615</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1396,13 +1396,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>77631.78038217922</v>
+        <v>79299.32063873248</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>77631.78038217922</v>
+        <v>79299.32063873248</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>-70388.23530817921</v>
+        <v>-72055.77556473248</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1461,13 +1461,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>77608.20594253513</v>
+        <v>79275.23981720538</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>77608.20594253513</v>
+        <v>79275.23981720538</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-77114.03514923617</v>
+        <v>-78781.06902390641</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1526,13 +1526,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>400901.9210290819</v>
+        <v>409513.3439406063</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>-76512.46219297579</v>
+        <v>-67901.03928145133</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-400901.9210290819</v>
+        <v>-409513.3439406063</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>212949426.0434853</v>
@@ -1595,13 +1595,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>58098.66881839281</v>
+        <v>59346.63541956928</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>58098.66881839281</v>
+        <v>59346.63541956928</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-18055.0913166206</v>
+        <v>-19303.05791779707</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1660,13 +1660,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>16003.61693690594</v>
+        <v>16347.37661060362</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>16003.61693690594</v>
+        <v>16347.37661060362</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>553.5460451558301</v>
+        <v>209.7863714581444</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1725,13 +1725,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>14717.14068513548</v>
+        <v>15033.26668962752</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>14717.14068513548</v>
+        <v>15033.26668962752</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-1541.721257046014</v>
+        <v>-1857.847261538047</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1790,13 +1790,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>3117.479341062812</v>
+        <v>3184.443183378462</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3117.479341062812</v>
+        <v>3184.443183378462</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>33.69279112026604</v>
+        <v>-33.27105119538358</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1855,13 +1855,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1619.324268299954</v>
+        <v>1654.107554120663</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1619.324268299954</v>
+        <v>1654.107554120663</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>131.2138794538295</v>
+        <v>96.43059363312064</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1920,13 +1920,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>1001.327733388663</v>
+        <v>1022.836377106592</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>1001.327733388663</v>
+        <v>1022.836377106592</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-1001.327733388663</v>
+        <v>-1022.836377106592</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1985,13 +1985,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>31.25685926279984</v>
+        <v>31.92826047062404</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>31.25685926279984</v>
+        <v>31.92826047062404</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-31.25685926279984</v>
+        <v>-31.92826047062404</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2050,13 +2050,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>3.104273009294972e-09</v>
+        <v>3.170953177968772e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3.104273009294972e-09</v>
+        <v>3.170953177968772e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-3.104273009294972e-09</v>
+        <v>-3.170953177968772e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.03628064516129032</v>
+        <v>0.03717741935483871</v>
       </c>
     </row>
     <row r="10">
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.03669555805697115</v>
+        <v>0.03751760106772383</v>
       </c>
     </row>
     <row r="11">
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.03679407153085185</v>
+        <v>0.03759893383144367</v>
       </c>
     </row>
     <row r="12">
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>-44.93212844692437</v>
+        <v>-36.8835054410062</v>
       </c>
     </row>
     <row r="13">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>365834.9611412594</v>
+        <v>300174.2874459205</v>
       </c>
     </row>
     <row r="15">
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3056810.760658033</v>
+        <v>3122471.434353372</v>
       </c>
     </row>
     <row r="17">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>365834.9611412594</v>
+        <v>300174.2874459205</v>
       </c>
     </row>
     <row r="19">
@@ -3037,7 +3037,7 @@
         <v>977923557.3838165</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2993539.099199175</v>
+        <v>3059199.772894514</v>
       </c>
     </row>
     <row r="21">
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3056810.760658033</v>
+        <v>3122471.434353372</v>
       </c>
     </row>
     <row r="25">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>6308194.513801275</v>
+        <v>6373855.187496614</v>
       </c>
     </row>
     <row r="28">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>7972910.096261334</v>
+        <v>8040239.473993795</v>
       </c>
     </row>
     <row r="31">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>3056810.760658033</v>
+        <v>3122471.434353372</v>
       </c>
     </row>
     <row r="32">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-4916099.3356033</v>
+        <v>-4917768.039640422</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -3664,16 +3664,16 @@
         <v>2</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.0366</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.0371433334913717</v>
+        <v>0.0376933334913717</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>106686.9212384756</v>
+        <v>108139.5666808547</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>264775.7056934781</v>
+        <v>266228.3511358572</v>
       </c>
     </row>
     <row r="8">
@@ -3713,16 +3713,16 @@
         <v>2</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.0366</v>
+        <v>0.0371</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0371433334913717</v>
+        <v>0.03760166682470503</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>106676.6521193884</v>
+        <v>107887.2433171195</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>264775.7056934781</v>
+        <v>265986.2968912093</v>
       </c>
     </row>
     <row r="9">
@@ -3762,16 +3762,16 @@
         <v>2</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0366</v>
+        <v>0.0371</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0371433334913717</v>
+        <v>0.03760166682470503</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>107821.7134858072</v>
+        <v>109032.3046835383</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>265932.3814586352</v>
+        <v>267142.9726563664</v>
       </c>
     </row>
     <row r="10">
@@ -3811,16 +3811,16 @@
         <v>2</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.0366</v>
+        <v>0.037</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0371433334913717</v>
+        <v>0.03751000015803836</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>106191.6704754877</v>
+        <v>107160.1861018527</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>264313.6137252979</v>
+        <v>265282.1293516629</v>
       </c>
     </row>
     <row r="11">
@@ -3860,16 +3860,16 @@
         <v>2</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0366</v>
+        <v>0.0369</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.0371433334913717</v>
+        <v>0.0374183334913717</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>100397.4197558812</v>
+        <v>101123.8384806092</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>258531.0011066858</v>
+        <v>259257.4198314138</v>
       </c>
     </row>
     <row r="12">
@@ -3909,16 +3909,16 @@
         <v>2</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.0366</v>
+        <v>0.0369</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0371433334913717</v>
+        <v>0.0374183334913717</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>100397.4197558812</v>
+        <v>101123.8384806092</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>258531.0011066858</v>
+        <v>259257.4198314138</v>
       </c>
     </row>
     <row r="13">
@@ -3958,16 +3958,16 @@
         <v>2</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0366</v>
+        <v>0.0369</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0371433334913717</v>
+        <v>0.0374183334913717</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>100397.4197558812</v>
+        <v>101123.8384806092</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>258531.0011066858</v>
+        <v>259257.4198314138</v>
       </c>
     </row>
     <row r="14">
@@ -4007,16 +4007,16 @@
         <v>2</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03739270863051299</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>97285.23058815987</v>
+        <v>98953.09423859511</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>246270.7043362921</v>
+        <v>247966.0219872215</v>
       </c>
     </row>
     <row r="15">
@@ -4056,16 +4056,16 @@
         <v>2</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03739270863051299</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>102463.129290677</v>
+        <v>104158.4469416064</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>251623.480097451</v>
+        <v>253318.7977483803</v>
       </c>
     </row>
     <row r="16">
@@ -4105,16 +4105,16 @@
         <v>2</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03739270863051299</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>75236.3185192144</v>
+        <v>76526.17433897371</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>221971.0412825704</v>
+        <v>223666.3589334998</v>
       </c>
     </row>
     <row r="17">
@@ -4154,16 +4154,16 @@
         <v>2</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03748437529717965</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>107692.8219477053</v>
+        <v>109630.2424637236</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>226879.365895768</v>
+        <v>228816.7864117863</v>
       </c>
     </row>
     <row r="18">
@@ -4203,16 +4203,16 @@
         <v>2</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03748437529717965</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>96971.86597365631</v>
+        <v>98871.77232365517</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>231849.8239491097</v>
+        <v>233787.244465128</v>
       </c>
     </row>
     <row r="19">
@@ -4252,16 +4252,16 @@
         <v>2</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03748437529717965</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>96971.86597365631</v>
+        <v>98871.77232365517</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>231849.8239491097</v>
+        <v>233787.244465128</v>
       </c>
     </row>
     <row r="20">
@@ -4301,16 +4301,16 @@
         <v>2</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.03675104196384631</v>
+        <v>0.03748437529717965</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>96971.86597365631</v>
+        <v>98871.77232365517</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>231849.8239491097</v>
+        <v>233787.244465128</v>
       </c>
     </row>
     <row r="21">
@@ -4350,16 +4350,16 @@
         <v>2</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.0372</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.03656770863051298</v>
+        <v>0.03748437529717965</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>101706.4343262186</v>
+        <v>104128.423511205</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>236818.906863795</v>
+        <v>239240.8960487814</v>
       </c>
     </row>
     <row r="22">
@@ -4399,16 +4399,16 @@
         <v>2</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.03656770863051298</v>
+        <v>0.03748437529717965</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>102676.3335262527</v>
+        <v>105098.3227112391</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>243254.2424155113</v>
+        <v>245676.2316004977</v>
       </c>
     </row>
     <row r="23">
@@ -4448,16 +4448,16 @@
         <v>2</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.0373</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.03656770863051298</v>
+        <v>0.03757604196384631</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>102662.9053310994</v>
+        <v>105326.9760497937</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>248707.8939991647</v>
+        <v>251371.964717859</v>
       </c>
     </row>
     <row r="24">
@@ -4497,16 +4497,16 @@
         <v>2</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.0373</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.03656770863051298</v>
+        <v>0.03757604196384631</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>97317.171635483</v>
+        <v>99951.87154193679</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>248708.9845113354</v>
+        <v>251373.0552300297</v>
       </c>
     </row>
     <row r="25">
@@ -4546,16 +4546,16 @@
         <v>2</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.0374</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.03656770863051298</v>
+        <v>0.03766770863051298</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>92387.83631709813</v>
+        <v>95116.348521183</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>248708.9845113354</v>
+        <v>251615.1154361312</v>
       </c>
     </row>
     <row r="26">
@@ -4595,16 +4595,16 @@
         <v>2</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.0374</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.03656770863051298</v>
+        <v>0.03766770863051298</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>92387.83631709813</v>
+        <v>95116.348521183</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>248708.9845113354</v>
+        <v>251615.1154361312</v>
       </c>
     </row>
     <row r="27">
@@ -4644,16 +4644,16 @@
         <v>2</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0362</v>
+        <v>0.0374</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.03656770863051298</v>
+        <v>0.03766770863051298</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>93765.46478037485</v>
+        <v>96534.66281740686</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>250236.0069547584</v>
+        <v>253142.1378795541</v>
       </c>
     </row>
     <row r="28">
@@ -4693,16 +4693,16 @@
         <v>2</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.036</v>
+        <v>0.0374</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.03638437529717965</v>
+        <v>0.03766770863051298</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>98296.56230374491</v>
+        <v>101687.3473740235</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>260767.7290082554</v>
+        <v>264158.514078534</v>
       </c>
     </row>
     <row r="29">
@@ -4742,16 +4742,16 @@
         <v>2</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.036</v>
+        <v>0.0374</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.03638437529717965</v>
+        <v>0.03766770863051298</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>95795.08985554657</v>
+        <v>99112.38208687022</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>266221.3805919088</v>
+        <v>269612.1656621874</v>
       </c>
     </row>
     <row r="30">
@@ -4791,16 +4791,16 @@
         <v>2</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.036</v>
+        <v>0.0373</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.03638437529717965</v>
+        <v>0.03757604196384631</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>95782.94715018995</v>
+        <v>98863.03518464576</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>271675.0321755622</v>
+        <v>274823.7570397393</v>
       </c>
     </row>
     <row r="31">
@@ -4840,16 +4840,16 @@
         <v>2</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.036</v>
+        <v>0.0373</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.03638437529717965</v>
+        <v>0.03757604196384631</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>93702.84270474337</v>
+        <v>96716.04091169375</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>274828.7134954759</v>
+        <v>277977.4383596529</v>
       </c>
     </row>
     <row r="32">
@@ -4889,16 +4889,16 @@
         <v>2</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.036</v>
+        <v>0.0373</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.03638437529717965</v>
+        <v>0.03757604196384631</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>94668.77300327882</v>
+        <v>97713.03258851371</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>281373.09539586</v>
+        <v>284521.820260037</v>
       </c>
     </row>
     <row r="33">
@@ -4938,16 +4938,16 @@
         <v>2</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.036</v>
+        <v>0.0373</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.03638437529717965</v>
+        <v>0.03757604196384631</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>95158.35989800739</v>
+        <v>98218.36310756316</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>281918.4605542253</v>
+        <v>285067.1854184024</v>
       </c>
     </row>
     <row r="34">
@@ -4987,16 +4987,16 @@
         <v>2</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.036</v>
+        <v>0.0373</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.03638437529717965</v>
+        <v>0.03757604196384631</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>95158.35989800739</v>
+        <v>98218.36310756316</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>281918.4605542253</v>
+        <v>285067.1854184024</v>
       </c>
     </row>
     <row r="35">
@@ -5036,16 +5036,16 @@
         <v>2</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.0358</v>
+        <v>0.0371</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.03620104196384632</v>
+        <v>0.03739270863051299</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>100342.1782243444</v>
+        <v>103491.4583414762</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>292924.2269816257</v>
+        <v>296073.5070987574</v>
       </c>
     </row>
     <row r="36">
@@ -5085,16 +5085,16 @@
         <v>2</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.0358</v>
+        <v>0.037</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.03620104196384632</v>
+        <v>0.03730104196384632</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>96020.33888090946</v>
+        <v>98885.35514591001</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>299359.5543609764</v>
+        <v>302266.7102778634</v>
       </c>
     </row>
     <row r="38">
@@ -5116,10 +5116,10 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="10" t="n">
-        <v>3056810.760658033</v>
+        <v>3122471.434353372</v>
       </c>
       <c r="O38" s="10" t="n">
-        <v>7972910.096261334</v>
+        <v>8040239.473993795</v>
       </c>
     </row>
   </sheetData>

--- a/reports/grove/2026-03/grove_settlement_march_2026.xlsx
+++ b/reports/grove/2026-03/grove_settlement_march_2026.xlsx
@@ -2923,7 +2923,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base rate (BR = SSR + 30bps), period avg</t>
+          <t>Base rate (BR = SSR (+) spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tbill_3m</t>
+          <t>tbill_3m→sofr@2026-07-23</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
+          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>
